--- a/data/dividends_info_20260831.xlsx
+++ b/data/dividends_info_20260831.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.47999954223633</v>
+        <v>43.01499938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2069917225104253</v>
+        <v>0.2092293415716251</v>
       </c>
       <c r="J2" t="n">
         <v>196</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.94999694824219</v>
+        <v>66.05000305175781</v>
       </c>
       <c r="I3" t="n">
-        <v>1.061410208327019</v>
+        <v>1.059803130442657</v>
       </c>
       <c r="J3" t="n">
         <v>175</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.47999954223633</v>
+        <v>43.01499938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2069917225104253</v>
+        <v>0.2092293415716251</v>
       </c>
       <c r="J6" t="n">
         <v>105</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.115000009536743</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.640661922118176</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>84</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.34499931335449</v>
+        <v>23.30500030517578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.156564608873416</v>
+        <v>1.158549652282287</v>
       </c>
       <c r="J8" t="n">
         <v>84</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.22999954223633</v>
+        <v>23.93000030517578</v>
       </c>
       <c r="I9" t="n">
-        <v>2.434997982445465</v>
+        <v>2.465524414859242</v>
       </c>
       <c r="J9" t="n">
         <v>84</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.869999885559082</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I10" t="n">
-        <v>3.407155091979209</v>
+        <v>3.395585815510971</v>
       </c>
       <c r="J10" t="n">
         <v>77</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.26000022888184</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="I11" t="n">
-        <v>4.483430699203134</v>
+        <v>4.440154587297886</v>
       </c>
       <c r="J11" t="n">
         <v>56</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.34499931335449</v>
+        <v>23.30500030517578</v>
       </c>
       <c r="I16" t="n">
-        <v>1.156564608873416</v>
+        <v>1.158549652282287</v>
       </c>
       <c r="J16" t="n">
         <v>21</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.00600004196167</v>
+        <v>2.003999948501587</v>
       </c>
       <c r="I17" t="n">
-        <v>2.841475513841946</v>
+        <v>2.844311450338087</v>
       </c>
       <c r="J17" t="n">
         <v>21</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>43.47999954223633</v>
+        <v>43.01499938964844</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2069917225104253</v>
+        <v>0.2092293415716251</v>
       </c>
       <c r="J18" t="n">
         <v>21</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.460000038146973</v>
+        <v>6.420000076293945</v>
       </c>
       <c r="I20" t="n">
-        <v>4.643962820874129</v>
+        <v>4.672897140729944</v>
       </c>
       <c r="J20" t="n">
         <v>14</v>
@@ -1627,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C244"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,7 +1922,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2119,14 +2119,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2143,7 +2143,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2194,7 +2194,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2204,14 +2204,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2228,12 +2228,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2262,12 +2262,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2296,12 +2296,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2313,29 +2313,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2347,29 +2347,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2398,12 +2398,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2415,46 +2415,46 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2466,29 +2466,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2500,46 +2500,46 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2551,12 +2551,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2568,97 +2568,97 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2670,12 +2670,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2687,12 +2687,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2704,29 +2704,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2738,29 +2738,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>MB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2772,12 +2772,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2789,46 +2789,46 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENTERA</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2840,12 +2840,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2857,80 +2857,80 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2942,12 +2942,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2976,29 +2976,29 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3010,29 +3010,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3078,29 +3078,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3112,12 +3112,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3146,12 +3146,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3163,12 +3163,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3180,12 +3180,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3197,29 +3197,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3231,12 +3231,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3248,29 +3248,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3282,12 +3282,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>ENTERA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3316,12 +3316,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3333,46 +3333,46 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3401,12 +3401,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3435,12 +3435,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3469,12 +3469,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3486,12 +3486,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3503,29 +3503,29 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3537,12 +3537,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3554,12 +3554,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3571,29 +3571,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3605,12 +3605,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3622,12 +3622,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3656,12 +3656,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,12 +3673,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3690,12 +3690,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3707,12 +3707,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3724,12 +3724,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3741,12 +3741,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3758,12 +3758,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3775,29 +3775,29 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3809,29 +3809,29 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3843,7 +3843,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3904,14 +3904,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3972,19 +3972,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3996,12 +3996,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4013,12 +4013,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4030,12 +4030,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4047,12 +4047,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4064,12 +4064,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4081,12 +4081,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4098,12 +4098,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4115,12 +4115,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4149,12 +4149,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4183,12 +4183,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4200,12 +4200,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4217,12 +4217,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4234,12 +4234,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4251,12 +4251,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4268,12 +4268,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4285,41 +4285,41 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4387,7 +4387,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4404,7 +4404,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4421,7 +4421,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4472,7 +4472,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4489,7 +4489,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4506,7 +4506,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4523,7 +4523,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4608,7 +4608,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4642,7 +4642,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4676,7 +4676,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4693,7 +4693,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4703,14 +4703,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4727,7 +4727,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4744,7 +4744,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4761,7 +4761,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4778,7 +4778,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4812,7 +4812,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4829,12 +4829,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4846,12 +4846,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4863,29 +4863,29 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4897,12 +4897,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4914,12 +4914,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4931,12 +4931,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4948,12 +4948,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4965,12 +4965,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4982,29 +4982,29 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5016,12 +5016,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5033,12 +5033,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5050,12 +5050,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5067,12 +5067,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5084,12 +5084,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5101,29 +5101,29 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5135,12 +5135,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5152,12 +5152,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5169,12 +5169,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5186,12 +5186,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5203,12 +5203,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5220,12 +5220,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5237,12 +5237,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5254,12 +5254,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5271,12 +5271,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5288,12 +5288,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5305,12 +5305,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5322,12 +5322,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5407,7 +5407,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5424,7 +5424,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5441,7 +5441,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5458,7 +5458,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5475,7 +5475,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5509,7 +5509,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5543,7 +5543,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5560,7 +5560,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5577,7 +5577,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5594,7 +5594,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5611,7 +5611,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5628,7 +5628,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5645,7 +5645,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5662,7 +5662,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5679,7 +5679,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5696,7 +5696,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5730,7 +5730,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5747,7 +5747,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5773,6 +5773,516 @@
         </is>
       </c>
       <c r="C244" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Leone Film Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>OPS ECOM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Valica S.p.A.</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>VNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Alia Mentis S.p.A.</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>B.F. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLASS EDITORI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Casta Diva Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CleanBnB S.p.A.</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Cogefeed S.p.A.</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Com.Tel S.p.A.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Cube Labs S.p.A.</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>DEODATO.GALLERY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>DESTINATION ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>OPT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>G.M. Leather S.p.A.</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ABC Company S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>AATECH S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>doxee S.p.A.</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Vivenda Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Vantea Smart S.p.A.</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Litix S.p.A.</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Lucisano Media Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>MEVIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>MONDO TV FRANCE</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>MONDO TV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Matica Fintec S.p.A.</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Met.Extra Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ACQUAZZURRA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Gentili Mosconi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
         <is>
           <t>Half Year Report</t>
         </is>
@@ -5802,7 +6312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5825,7 +6335,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5842,7 +6352,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5859,7 +6369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5876,7 +6386,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5893,7 +6403,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5910,7 +6420,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5927,7 +6437,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5944,7 +6454,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5961,7 +6471,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5978,7 +6488,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5987,788 +6497,6 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Emma Villas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Execus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>FRANCHETTI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>First Point S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>G.M. Leather S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Gentili Mosconi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>IDNTT S.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>KALEON S.P.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Leone Film Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Litix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Lucisano Media Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MEVIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MONDO TV FRANCE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MONDO TV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Matica Fintec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Met.Extra Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>OPT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Officina Stellare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PLC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Piu' Medical S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Portobello S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Pozzi Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ROSETTI MARINO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Reway Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Solid World Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>TRAWELL CO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>The Italian Sea Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Valica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Vantea Smart S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Vivenda Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>doxee S.p.A.</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
         <is>
           <t>Half Year Report</t>
         </is>
